--- a/作業担当.xlsx
+++ b/作業担当.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Desktop\2B_Team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Desktop\Team\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -116,31 +116,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤーの挙動スクリプト作成、回復パーティクル作成、プレイヤーの移動演出作成</t>
-    <rPh sb="6" eb="8">
-      <t>キョドウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>カイフク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>福住</t>
     <rPh sb="0" eb="2">
       <t>フクスミ</t>
@@ -182,6 +157,22 @@
       <t>サクセイ</t>
     </rPh>
     <rPh sb="39" eb="41">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの挙動スクリプト作成、回復パーティクル作成</t>
+    <rPh sb="6" eb="8">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
       <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -548,23 +539,23 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
         <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
